--- a/data/baidu/china_disaster.xlsx
+++ b/data/baidu/china_disaster.xlsx
@@ -580,24 +580,30 @@
           <t>https://movie.douban.com/subject/35267208/</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>34837.71428571428</v>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>流浪地球2</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>流浪地球2</t>
+        </is>
+      </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -657,24 +663,30 @@
           <t>https://movie.douban.com/subject/6011805/</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>12356.85714285714</v>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>一九四二</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>一九四二</t>
+        </is>
+      </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -734,24 +746,30 @@
           <t>https://movie.douban.com/subject/26266893/</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>53317</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>流浪地球</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>流浪地球</t>
+        </is>
+      </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -814,16 +832,24 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>唐山大地震</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>唐山大地震</t>
+        </is>
+      </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
@@ -888,24 +914,30 @@
           <t>https://movie.douban.com/subject/20443013/</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>8721</v>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>救火英雄</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>救火英雄</t>
+        </is>
+      </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -968,16 +1000,24 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>紧急迫降</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>紧急迫降</t>
+        </is>
+      </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
@@ -1042,24 +1082,30 @@
           <t>https://movie.douban.com/subject/35087699/</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>14027.71428571429</v>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>中国医生</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>中国医生</t>
+        </is>
+      </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1119,24 +1165,30 @@
           <t>https://movie.douban.com/subject/22266320/</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>4696</v>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>深海浩劫</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>深海浩劫</t>
+        </is>
+      </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1196,24 +1248,30 @@
           <t>https://movie.douban.com/subject/36421884/</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>8458.285714285714</v>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>焚城</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>焚城</t>
+        </is>
+      </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1273,24 +1331,30 @@
           <t>https://movie.douban.com/subject/3742937/</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>39461.71428571428</v>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>超级战舰</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>超级战舰</t>
+        </is>
+      </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1350,24 +1414,30 @@
           <t>https://movie.douban.com/subject/30295905/</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>71114.28571428571</v>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>中国机长</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>中国机长</t>
+        </is>
+      </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1430,16 +1500,24 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>十万火急</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>十万火急</t>
+        </is>
+      </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
@@ -1504,24 +1582,30 @@
           <t>https://movie.douban.com/subject/10763157/</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>3978.428571428572</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>逃出生天</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>逃出生天</t>
+        </is>
+      </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1581,24 +1665,30 @@
           <t>https://movie.douban.com/subject/25956520/</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>26542</v>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>太平轮(下)·彼岸</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>太平轮</t>
+        </is>
+      </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1658,24 +1748,30 @@
           <t>https://movie.douban.com/subject/30221757/</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>44311.42857142857</v>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>烈火英雄</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>烈火英雄</t>
+        </is>
+      </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1735,24 +1831,30 @@
           <t>https://movie.douban.com/subject/25890017/</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>42276.14285714286</v>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>哥斯拉2：怪兽之王</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>哥斯拉2</t>
+        </is>
+      </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1812,24 +1914,30 @@
           <t>https://movie.douban.com/subject/35192609/</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>6363.285714285715</v>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>绝地追击</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>绝地追击</t>
+        </is>
+      </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1889,21 +1997,27 @@
           <t>https://movie.douban.com/subject/36642518/</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>大场面</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>大场面</t>
+        </is>
+      </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1966,24 +2080,30 @@
           <t>https://movie.douban.com/subject/26342391/</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>7117.571428571428</v>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>紧急救援</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>紧急救援</t>
+        </is>
+      </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -2043,24 +2163,30 @@
           <t>https://movie.douban.com/subject/36459360/</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>4702.285714285715</v>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>出入平安</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>出入平安</t>
+        </is>
+      </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -2120,24 +2246,30 @@
           <t>https://movie.douban.com/subject/35231370/</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>8311.714285714286</v>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>峰爆</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>峰爆</t>
+        </is>
+      </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -2200,16 +2332,24 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>惊涛骇浪</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>惊涛骇浪</t>
+        </is>
+      </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
@@ -2274,24 +2414,30 @@
           <t>https://movie.douban.com/subject/35497671/</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>3808.714285714286</v>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>危机航线</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>危机航线</t>
+        </is>
+      </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -2351,24 +2497,30 @@
           <t>https://movie.douban.com/subject/10810268/</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>987</v>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>冰雪11天</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>冰雪11天</t>
+        </is>
+      </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -2428,24 +2580,30 @@
           <t>https://movie.douban.com/subject/26825482/</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>9913.857142857143</v>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>月球陨落</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>月球陨落</t>
+        </is>
+      </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -2505,24 +2663,30 @@
           <t>https://movie.douban.com/subject/36789117/</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>6513</v>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>狂蟒之灾</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>狂蟒之灾</t>
+        </is>
+      </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -2582,24 +2746,30 @@
           <t>https://movie.douban.com/subject/10527288/</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>7068.142857142857</v>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>百万巨鳄</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>百万巨鳄</t>
+        </is>
+      </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -2659,24 +2829,30 @@
           <t>https://movie.douban.com/subject/5324813/</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>460.4285714285714</v>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>天际浩劫2</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>天际浩劫2</t>
+        </is>
+      </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -2736,24 +2912,30 @@
           <t>https://movie.douban.com/subject/35215919/</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>9029.857142857143</v>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>惊天救援</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>惊天救援</t>
+        </is>
+      </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -2816,16 +2998,24 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>超强台风</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>超强台风</t>
+        </is>
+      </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
@@ -2890,24 +3080,30 @@
           <t>https://movie.douban.com/subject/5298766/</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>722.7142857142857</v>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>幸存日</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>幸存日</t>
+        </is>
+      </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -2967,24 +3163,30 @@
           <t>https://movie.douban.com/subject/34800551/</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>394.5714285714286</v>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>大地震</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>大地震</t>
+        </is>
+      </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -3047,16 +3249,24 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>爬满青藤的木屋</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>爬满青藤的木屋</t>
+        </is>
+      </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
@@ -3121,21 +3331,27 @@
           <t>https://movie.douban.com/subject/38222804/</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>大蛇5：怪兽都市</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>大蛇5</t>
+        </is>
+      </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3198,21 +3414,27 @@
           <t>https://movie.douban.com/subject/37528113/</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>工厂蛇患</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>工厂蛇患</t>
+        </is>
+      </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3278,16 +3500,24 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>你没有十六岁</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>你没有十六岁</t>
+        </is>
+      </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
@@ -3355,16 +3585,24 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>山清水秀</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>山清水秀</t>
+        </is>
+      </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
@@ -3428,16 +3666,24 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>爆炸性新闻</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>爆炸性新闻</t>
+        </is>
+      </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
@@ -3505,16 +3751,24 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>南海岛血书</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>南海岛血书</t>
+        </is>
+      </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
@@ -3579,21 +3833,27 @@
           <t>https://movie.douban.com/subject/35295370/</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>狂虎危城</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>狂虎危城</t>
+        </is>
+      </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3655,16 +3915,24 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>空谷十年</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>空谷十年</t>
+        </is>
+      </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
@@ -3729,21 +3997,27 @@
           <t>https://movie.douban.com/subject/27595272/</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>冰峰暴</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>冰峰暴</t>
+        </is>
+      </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3809,16 +4083,24 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2224670317, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>天·火</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>天·火</t>
+        </is>
+      </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
@@ -3886,16 +4168,24 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2224876725, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>亲爱的，我要和别人结婚了</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>亲爱的，我要和别人结婚了</t>
+        </is>
+      </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
@@ -3960,21 +4250,27 @@
           <t>https://movie.douban.com/subject/35248741/</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>沙丘虫暴</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>沙丘虫暴</t>
+        </is>
+      </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4037,21 +4333,27 @@
           <t>https://movie.douban.com/subject/35176462/</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>怒海狂蛛</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>怒海狂蛛</t>
+        </is>
+      </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4114,21 +4416,27 @@
           <t>https://movie.douban.com/subject/35295541/</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>黄河巨蛇事件</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>黄河巨蛇事件</t>
+        </is>
+      </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4194,16 +4502,24 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2225840516, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>怪兽湖</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>怪兽湖</t>
+        </is>
+      </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
@@ -4268,24 +4584,30 @@
           <t>https://movie.douban.com/subject/35496693/</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>732.8571428571429</v>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>深海蛇难</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>深海蛇难</t>
+        </is>
+      </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -4345,24 +4667,30 @@
           <t>https://movie.douban.com/subject/34868338/</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>681.2857142857143</v>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>蟑潮</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>蟑潮</t>
+        </is>
+      </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4422,24 +4750,30 @@
           <t>https://movie.douban.com/subject/34807467/</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="n">
+        <v>2922.285714285714</v>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>大雪怪</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>大雪怪</t>
+        </is>
+      </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -4499,21 +4833,27 @@
           <t>https://movie.douban.com/subject/35083386/</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>蛇岛狂蟒</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>蛇岛狂蟒</t>
+        </is>
+      </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -4576,21 +4916,27 @@
           <t>https://movie.douban.com/subject/35152517/</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>狂鳄海啸</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>狂鳄海啸</t>
+        </is>
+      </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -4653,24 +4999,30 @@
           <t>https://movie.douban.com/subject/35203362/</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>1804</v>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>终极台风</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>终极台风</t>
+        </is>
+      </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -4733,16 +5085,24 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2227703149, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>全城风暴</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>全城风暴</t>
+        </is>
+      </c>
       <c r="T56" t="n">
         <v>0</v>
       </c>
@@ -4807,24 +5167,30 @@
           <t>https://movie.douban.com/subject/35915123/</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>584.1428571428571</v>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>巨蛇闯女校</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>巨蛇闯女校</t>
+        </is>
+      </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -4884,24 +5250,30 @@
           <t>https://movie.douban.com/subject/35005710/</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>4591.285714285715</v>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>变异狂蟒2</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>变异狂蟒2</t>
+        </is>
+      </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -4961,24 +5333,30 @@
           <t>https://movie.douban.com/subject/35027723/</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>1115.142857142857</v>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>火星异变</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>火星异变</t>
+        </is>
+      </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -5038,21 +5416,27 @@
           <t>https://movie.douban.com/subject/35860951/</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>环线</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>环线</t>
+        </is>
+      </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -5115,24 +5499,30 @@
           <t>https://movie.douban.com/subject/35196786/</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>659.7142857142857</v>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>大章鱼</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>大章鱼</t>
+        </is>
+      </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -5192,24 +5582,30 @@
           <t>https://movie.douban.com/subject/35237993/</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>658.7142857142857</v>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>搜救</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>搜救</t>
+        </is>
+      </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -5269,24 +5665,30 @@
           <t>https://movie.douban.com/subject/35295114/</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>3767.571428571428</v>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>末日救援</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>末日救援</t>
+        </is>
+      </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -5346,24 +5748,30 @@
           <t>https://movie.douban.com/subject/25715111/</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>3770</v>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>绝命航班</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>绝命航班</t>
+        </is>
+      </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -5423,24 +5831,30 @@
           <t>https://movie.douban.com/subject/35099279/</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>4081.428571428572</v>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>陆行鲨</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>陆行鲨</t>
+        </is>
+      </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -5500,24 +5914,30 @@
           <t>https://movie.douban.com/subject/25958914/</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>4316.571428571428</v>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>食人虫</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>食人虫</t>
+        </is>
+      </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -5577,24 +5997,30 @@
           <t>https://movie.douban.com/subject/34954819/</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>6679</v>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>巨鳄岛</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>巨鳄岛</t>
+        </is>
+      </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
